--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47B.xlsx
@@ -103,7 +103,7 @@
     <t>Fecha de término del periodo que se informa</t>
   </si>
   <si>
-    <t>Temática de las preguntas frecuentes</t>
+    <t>Temática de las preguntas frecuentes (Redactada con perspectiva de género)</t>
   </si>
   <si>
     <t>Planteamiento de las preguntas frecuentes</t>
@@ -130,28 +130,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>0806E41392AB361304AEBB092C332689</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>59B8CE75C6C19C77196855C98910F2E5</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Área de Transparencia</t>
-  </si>
-  <si>
-    <t>11/01/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre del 2022 al 31 de diciembre del 2022, el Colegio de Bachilleres del Estado de Tlaxcala no se generó política en referencia a este tema.</t>
+    <t>Transparencia y Archivo</t>
+  </si>
+  <si>
+    <t>17/01/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero del 2023 al 31 de marzo del 2023, el Colegio de Bachilleres del Estado de Tlaxcala no se generó política en referencia a este tema.</t>
   </si>
 </sst>
 </file>
@@ -547,11 +547,11 @@
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="66.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="53.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40.7109375" bestFit="1" customWidth="1"/>
@@ -559,7 +559,7 @@
     <col min="10" max="10" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="255" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="140.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
